--- a/nr-translate-en/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/nr-translate-en/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:31:08+00:00</t>
+    <t>2026-06-18T12:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
